--- a/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-01_New_Business_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-01_New_Business_v1.0.xlsx
@@ -2030,7 +2030,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and demo user for built BRDs)</t>
+          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Demo seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Demo users of TD-NB-01; a second approver available.</t>
+          <t>SIT/UAT users of TD-NB-01; a second approver available.</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Catalogue TD-NB-03; demo records TD-NB-04 to TD-NB-06.</t>
+          <t>Catalogue TD-NB-03; seed records TD-NB-04 to TD-NB-06.</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>All demo data; targets and variant TD-NB-10.</t>
+          <t>All seed data; targets and variant TD-NB-10.</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J20" s="12" t="inlineStr">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J22" s="12" t="inlineStr">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -13265,7 +13265,7 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J32" s="12" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J34" s="12" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
@@ -13565,7 +13565,7 @@
       <c r="I35" s="12" t="inlineStr">
         <is>
           <t>An account without stage movement for 5 days (NB_STALLED_DAYS = 5).
-Data: TD-NB-06 Demo accounts</t>
+Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J36" s="12" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>PROCESSING_TL – Processing TL (demo user proctl)</t>
+          <t>PROCESSING_TL – Processing TL (SIT/UAT user proctl)</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -13718,7 +13718,7 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>PROCESSING_TL – Processing TL (demo user proctl)</t>
+          <t>PROCESSING_TL – Processing TL (SIT/UAT user proctl)</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
@@ -13872,7 +13872,7 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
@@ -13945,7 +13945,7 @@
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J40" s="12" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J41" s="12" t="inlineStr">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J42" s="12" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J44" s="12" t="inlineStr">
@@ -14311,7 +14311,7 @@
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J45" s="12" t="inlineStr">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>A Word file cannot be protected</t>
+          <t>A CSV file cannot be protected</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -14398,18 +14398,18 @@
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>1. Send a message with a .docx attachment through the messaging API used by the send dialog.</t>
+          <t>1. Send a message with a .csv attachment through the messaging API used by the send dialog.</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
           <t>Refused.
-Message "letter.docx cannot be password protected (only PDF and Excel files can)" (DOCUMENT_NOT_PROTECTABLE).</t>
+Message "notes.csv cannot be password protected. Send it as PDF, Excel or Word" (DOCUMENT_NOT_PROTECTABLE).</t>
         </is>
       </c>
       <c r="L46" s="12" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J47" s="12" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
@@ -14630,7 +14630,7 @@
       <c r="I49" s="12" t="inlineStr">
         <is>
           <t>The relay refuses one address (set up by the test lead).
-Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J49" s="12" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H50" s="12" t="inlineStr">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J50" s="12" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J51" s="12" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J52" s="12" t="inlineStr">
@@ -14927,7 +14927,7 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H53" s="12" t="inlineStr">
@@ -14938,7 +14938,7 @@
       <c r="I53" s="12" t="inlineStr">
         <is>
           <t>mkttl created and submitted a quotation.
-Data: TD-NB-04 Demo quotations and requests; TD-NB-05 Demo proposal requests (PRF)</t>
+Data: TD-NB-04 Seed quotations and requests; TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J53" s="12" t="inlineStr">
@@ -15005,7 +15005,7 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
@@ -15016,7 +15016,7 @@
       <c r="I54" s="12" t="inlineStr">
         <is>
           <t>mkttl created and submitted a PRF.
-Data: TD-NB-04 Demo quotations and requests; TD-NB-05 Demo proposal requests (PRF)</t>
+Data: TD-NB-04 Seed quotations and requests; TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J54" s="12" t="inlineStr">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
@@ -15094,7 +15094,7 @@
       <c r="I55" s="12" t="inlineStr">
         <is>
           <t>A PRF in QS_FOR_APPROVAL prepared by tsu.
-Data: TD-NB-04 Demo quotations and requests; TD-NB-05 Demo proposal requests (PRF)</t>
+Data: TD-NB-04 Seed quotations and requests; TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J55" s="12" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
@@ -15170,7 +15170,7 @@
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J56" s="12" t="inlineStr">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J57" s="12" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J58" s="12" t="inlineStr">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J59" s="12" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J60" s="12" t="inlineStr">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J61" s="12" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr">
@@ -15626,7 +15626,7 @@
       </c>
       <c r="I62" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J62" s="12" t="inlineStr">
@@ -15692,7 +15692,7 @@
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
@@ -15702,7 +15702,7 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J63" s="12" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="I64" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J64" s="12" t="inlineStr">
@@ -15846,7 +15846,7 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H65" s="12" t="inlineStr">
@@ -15856,7 +15856,7 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J65" s="12" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr">
@@ -15933,7 +15933,7 @@
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J66" s="12" t="inlineStr">
@@ -16000,7 +16000,7 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H67" s="12" t="inlineStr">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J67" s="12" t="inlineStr">
@@ -16077,7 +16077,7 @@
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H68" s="12" t="inlineStr">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J68" s="12" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-12 Documents to upload; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J69" s="12" t="inlineStr">
@@ -16231,7 +16231,7 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H70" s="12" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-08 Demo issuance</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J70" s="12" t="inlineStr">
@@ -16307,7 +16307,7 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr">
@@ -16317,7 +16317,7 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-08 Demo issuance</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J71" s="12" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H72" s="12" t="inlineStr">
@@ -16390,7 +16390,7 @@
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-08 Demo issuance</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J72" s="12" t="inlineStr">
@@ -16456,7 +16456,7 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H73" s="12" t="inlineStr">
@@ -16467,7 +16467,7 @@
       <c r="I73" s="12" t="inlineStr">
         <is>
           <t>The DBA changes the stored bytes of one test file in SIT.
-Data: TD-NB-02 Demo clients; TD-NB-08 Demo issuance</t>
+Data: TD-NB-02 Seed clients; TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J73" s="12" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H74" s="12" t="inlineStr">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H75" s="12" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H77" s="12" t="inlineStr">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H78" s="12" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
@@ -16995,7 +16995,7 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H80" s="12" t="inlineStr">
@@ -17072,7 +17072,7 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H81" s="12" t="inlineStr">
@@ -17082,7 +17082,7 @@
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-08 Demo issuance</t>
+          <t>Data: TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J81" s="12" t="inlineStr">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H82" s="12" t="inlineStr">
@@ -17154,7 +17154,7 @@
       </c>
       <c r="I82" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-08 Demo issuance</t>
+          <t>Data: TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J82" s="12" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H83" s="12" t="inlineStr">
@@ -17230,7 +17230,7 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J83" s="12" t="inlineStr">
@@ -17292,7 +17292,7 @@
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H84" s="12" t="inlineStr">
@@ -17302,7 +17302,7 @@
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J84" s="12" t="inlineStr">
@@ -17364,7 +17364,7 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J85" s="12" t="inlineStr">
@@ -17394,7 +17394,7 @@
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>CrmAdminApiIT#demoDataShowsTheClientBannerDuplicatesAndOverdueKyc</t>
+          <t>CrmAdminApiIT#seedDataShowsTheClientBannerDuplicatesAndOverdueKyc</t>
         </is>
       </c>
       <c r="N85" s="27" t="inlineStr">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H86" s="12" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J86" s="12" t="inlineStr">
@@ -17513,7 +17513,7 @@
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H87" s="12" t="inlineStr">
@@ -17589,7 +17589,7 @@
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H89" s="12" t="inlineStr">
@@ -17743,7 +17743,7 @@
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H90" s="12" t="inlineStr">
@@ -17820,7 +17820,7 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H91" s="12" t="inlineStr">
@@ -17897,7 +17897,7 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H92" s="12" t="inlineStr">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H93" s="12" t="inlineStr">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H94" s="12" t="inlineStr">
@@ -18128,7 +18128,7 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H95" s="12" t="inlineStr">
@@ -18138,7 +18138,7 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J95" s="12" t="inlineStr">
@@ -18204,7 +18204,7 @@
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H96" s="12" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J96" s="12" t="inlineStr">
@@ -18281,7 +18281,7 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H97" s="12" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J97" s="12" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H98" s="12" t="inlineStr">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J98" s="12" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J99" s="12" t="inlineStr">
@@ -18509,7 +18509,7 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H100" s="12" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J100" s="12" t="inlineStr">
@@ -18585,7 +18585,7 @@
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H101" s="12" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-12 Documents to upload; TD-NB-14 New records keyed in the test</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-12 Documents to upload; TD-NB-14 New records keyed in the test</t>
         </is>
       </c>
       <c r="J101" s="12" t="inlineStr">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H102" s="12" t="inlineStr">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="I102" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-12 Documents to upload; TD-NB-14 New records keyed in the test</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-12 Documents to upload; TD-NB-14 New records keyed in the test</t>
         </is>
       </c>
       <c r="J102" s="12" t="inlineStr">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H103" s="12" t="inlineStr">
@@ -18750,7 +18750,7 @@
       <c r="I103" s="12" t="inlineStr">
         <is>
           <t>mkttl created the prospect and submitted its KYC.
-Data: TD-NB-02 Demo clients; TD-NB-12 Documents to upload; TD-NB-14 New records keyed in the test</t>
+Data: TD-NB-02 Seed clients; TD-NB-12 Documents to upload; TD-NB-14 New records keyed in the test</t>
         </is>
       </c>
       <c r="J103" s="12" t="inlineStr">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H104" s="12" t="inlineStr">
@@ -18827,7 +18827,7 @@
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-12 Documents to upload; TD-NB-14 New records keyed in the test</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-12 Documents to upload; TD-NB-14 New records keyed in the test</t>
         </is>
       </c>
       <c r="J104" s="12" t="inlineStr">
@@ -18895,7 +18895,7 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H105" s="12" t="inlineStr">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-12 Documents to upload; TD-NB-14 New records keyed in the test</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-12 Documents to upload; TD-NB-14 New records keyed in the test</t>
         </is>
       </c>
       <c r="J105" s="12" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H106" s="12" t="inlineStr">
@@ -18983,7 +18983,7 @@
       <c r="I106" s="12" t="inlineStr">
         <is>
           <t>An accepted quotation of prospect PR-2026-000007.
-Data: TD-NB-04 Demo quotations and requests</t>
+Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J106" s="12" t="inlineStr">
@@ -19050,7 +19050,7 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H107" s="12" t="inlineStr">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-12 Documents to upload; TD-NB-14 New records keyed in the test</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-12 Documents to upload; TD-NB-14 New records keyed in the test</t>
         </is>
       </c>
       <c r="J107" s="12" t="inlineStr">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H108" s="12" t="inlineStr">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H109" s="12" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H110" s="12" t="inlineStr">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H111" s="12" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J111" s="12" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H112" s="12" t="inlineStr">
@@ -19442,7 +19442,7 @@
       </c>
       <c r="I112" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J112" s="12" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H113" s="12" t="inlineStr">
@@ -19518,7 +19518,7 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J113" s="12" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H114" s="12" t="inlineStr">
@@ -19595,7 +19595,7 @@
       </c>
       <c r="I114" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J114" s="12" t="inlineStr">
@@ -19662,7 +19662,7 @@
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H115" s="12" t="inlineStr">
@@ -19672,7 +19672,7 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J115" s="12" t="inlineStr">
@@ -19735,7 +19735,7 @@
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H116" s="12" t="inlineStr">
@@ -19745,7 +19745,7 @@
       </c>
       <c r="I116" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J116" s="12" t="inlineStr">
@@ -19765,7 +19765,7 @@
       </c>
       <c r="M116" s="12" t="inlineStr">
         <is>
-          <t>CrmAdminApiIT#demoDataShowsTheClientBannerDuplicatesAndOverdueKyc</t>
+          <t>CrmAdminApiIT#seedDataShowsTheClientBannerDuplicatesAndOverdueKyc</t>
         </is>
       </c>
       <c r="N116" s="27" t="inlineStr">
@@ -19811,7 +19811,7 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
@@ -19821,12 +19821,12 @@
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J117" s="12" t="inlineStr">
         <is>
-          <t>1. Open the demo client whose KYC review date has passed.</t>
+          <t>1. Open the seed client whose KYC review date has passed.</t>
         </is>
       </c>
       <c r="K117" s="12" t="inlineStr">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H118" s="12" t="inlineStr">
@@ -19897,7 +19897,7 @@
       </c>
       <c r="I118" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J118" s="12" t="inlineStr">
@@ -19963,7 +19963,7 @@
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H119" s="12" t="inlineStr">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J119" s="12" t="inlineStr">
@@ -20039,7 +20039,7 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H120" s="12" t="inlineStr">
@@ -20049,7 +20049,7 @@
       </c>
       <c r="I120" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J120" s="12" t="inlineStr">
@@ -20115,7 +20115,7 @@
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H121" s="12" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J121" s="12" t="inlineStr">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H122" s="12" t="inlineStr">
@@ -20198,7 +20198,7 @@
       </c>
       <c r="I122" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J122" s="12" t="inlineStr">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H123" s="12" t="inlineStr">
@@ -20274,7 +20274,7 @@
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
@@ -20340,7 +20340,7 @@
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H124" s="12" t="inlineStr">
@@ -20350,7 +20350,7 @@
       </c>
       <c r="I124" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J124" s="12" t="inlineStr">
@@ -20417,7 +20417,7 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H125" s="12" t="inlineStr">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J125" s="12" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H126" s="12" t="inlineStr">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="I126" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J126" s="12" t="inlineStr">
@@ -20571,7 +20571,7 @@
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H127" s="12" t="inlineStr">
@@ -20581,7 +20581,7 @@
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="J127" s="12" t="inlineStr">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H128" s="12" t="inlineStr">
@@ -20657,7 +20657,7 @@
       </c>
       <c r="I128" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="J128" s="12" t="inlineStr">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H129" s="12" t="inlineStr">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
@@ -20796,7 +20796,7 @@
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H130" s="12" t="inlineStr">
@@ -20806,7 +20806,7 @@
       </c>
       <c r="I130" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="J130" s="12" t="inlineStr">
@@ -20873,7 +20873,7 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H131" s="12" t="inlineStr">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="J131" s="12" t="inlineStr">
@@ -20946,7 +20946,7 @@
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H132" s="12" t="inlineStr">
@@ -20956,7 +20956,7 @@
       </c>
       <c r="I132" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="J132" s="12" t="inlineStr">
@@ -21023,7 +21023,7 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
@@ -21033,7 +21033,7 @@
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="J133" s="12" t="inlineStr">
@@ -21100,7 +21100,7 @@
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H134" s="12" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="I134" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J134" s="12" t="inlineStr">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H135" s="12" t="inlineStr">
@@ -21186,7 +21186,7 @@
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J135" s="12" t="inlineStr">
@@ -21252,7 +21252,7 @@
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H136" s="12" t="inlineStr">
@@ -21262,7 +21262,7 @@
       </c>
       <c r="I136" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J136" s="12" t="inlineStr">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
@@ -21339,7 +21339,7 @@
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J137" s="12" t="inlineStr">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H138" s="12" t="inlineStr">
@@ -21413,7 +21413,7 @@
       <c r="I138" s="12" t="inlineStr">
         <is>
           <t>ao is the maker of QT-2026-900002.
-Data: TD-NB-04 Demo quotations and requests</t>
+Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J138" s="12" t="inlineStr">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
@@ -21489,7 +21489,7 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J139" s="12" t="inlineStr">
@@ -21556,7 +21556,7 @@
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H140" s="12" t="inlineStr">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="I140" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J140" s="12" t="inlineStr">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
@@ -21638,7 +21638,7 @@
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
@@ -21701,7 +21701,7 @@
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H142" s="12" t="inlineStr">
@@ -21712,7 +21712,7 @@
       <c r="I142" s="12" t="inlineStr">
         <is>
           <t>Three approved quotations of two clients (for example QT-2026-900003 and two approved in this cycle).
-Data: TD-NB-04 Demo quotations and requests</t>
+Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J142" s="12" t="inlineStr">
@@ -21778,7 +21778,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
@@ -21788,7 +21788,7 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J143" s="12" t="inlineStr">
@@ -21855,7 +21855,7 @@
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H144" s="12" t="inlineStr">
@@ -21865,7 +21865,7 @@
       </c>
       <c r="I144" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J144" s="12" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H145" s="12" t="inlineStr">
@@ -21943,7 +21943,7 @@
       <c r="I145" s="12" t="inlineStr">
         <is>
           <t>A sent quotation of CL-2026-000001 with risk groups 1 and 2.
-Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J145" s="12" t="inlineStr">
@@ -22010,7 +22010,7 @@
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H146" s="12" t="inlineStr">
@@ -22020,7 +22020,7 @@
       </c>
       <c r="I146" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J146" s="12" t="inlineStr">
@@ -22087,7 +22087,7 @@
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H147" s="12" t="inlineStr">
@@ -22097,7 +22097,7 @@
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J147" s="12" t="inlineStr">
@@ -22164,7 +22164,7 @@
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H148" s="12" t="inlineStr">
@@ -22174,7 +22174,7 @@
       </c>
       <c r="I148" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J148" s="12" t="inlineStr">
@@ -22237,7 +22237,7 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H149" s="12" t="inlineStr">
@@ -22313,7 +22313,7 @@
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H150" s="12" t="inlineStr">
@@ -22389,7 +22389,7 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H151" s="12" t="inlineStr">
@@ -22465,7 +22465,7 @@
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H152" s="12" t="inlineStr">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H153" s="12" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H154" s="12" t="inlineStr">
@@ -22621,12 +22621,12 @@
       </c>
       <c r="I154" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-07 Demo placement and billing; TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-07 Seed placement and billing; TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J154" s="12" t="inlineStr">
         <is>
-          <t>1. Open QT-2026-900006; follow its account; open the account's slip and invoice (or a booked demo account and its quotation).</t>
+          <t>1. Open QT-2026-900006; follow its account; open the account's slip and invoice (or a booked seed account and its quotation).</t>
         </is>
       </c>
       <c r="K154" s="12" t="inlineStr">
@@ -22687,7 +22687,7 @@
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H155" s="12" t="inlineStr">
@@ -22697,7 +22697,7 @@
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-07 Demo placement and billing; TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-07 Seed placement and billing; TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J155" s="12" t="inlineStr">
@@ -22763,7 +22763,7 @@
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H156" s="12" t="inlineStr">
@@ -22773,7 +22773,7 @@
       </c>
       <c r="I156" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-07 Demo placement and billing; TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-07 Seed placement and billing; TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J156" s="12" t="inlineStr">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H157" s="12" t="inlineStr">
@@ -22850,7 +22850,7 @@
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-07 Demo placement and billing; TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-07 Seed placement and billing; TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J157" s="12" t="inlineStr">
@@ -22917,7 +22917,7 @@
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H158" s="12" t="inlineStr">
@@ -22927,7 +22927,7 @@
       </c>
       <c r="I158" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J158" s="12" t="inlineStr">
@@ -22993,7 +22993,7 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H159" s="12" t="inlineStr">
@@ -23003,7 +23003,7 @@
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J159" s="12" t="inlineStr">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H160" s="12" t="inlineStr">
@@ -23080,7 +23080,7 @@
       </c>
       <c r="I160" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J160" s="12" t="inlineStr">
@@ -23143,7 +23143,7 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr">
@@ -23153,7 +23153,7 @@
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
@@ -23220,7 +23220,7 @@
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H162" s="12" t="inlineStr">
@@ -23230,7 +23230,7 @@
       </c>
       <c r="I162" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J162" s="12" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H163" s="12" t="inlineStr">
@@ -23303,7 +23303,7 @@
       </c>
       <c r="I163" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J163" s="12" t="inlineStr">
@@ -23370,7 +23370,7 @@
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H164" s="12" t="inlineStr">
@@ -23380,7 +23380,7 @@
       </c>
       <c r="I164" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J164" s="12" t="inlineStr">
@@ -23447,7 +23447,7 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H165" s="12" t="inlineStr">
@@ -23457,7 +23457,7 @@
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J165" s="12" t="inlineStr">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H166" s="12" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="I166" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J166" s="12" t="inlineStr">
@@ -23597,7 +23597,7 @@
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H167" s="12" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J167" s="12" t="inlineStr">
@@ -23673,7 +23673,7 @@
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H168" s="12" t="inlineStr">
@@ -23683,7 +23683,7 @@
       </c>
       <c r="I168" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J168" s="12" t="inlineStr">
@@ -23746,7 +23746,7 @@
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H169" s="12" t="inlineStr">
@@ -23756,7 +23756,7 @@
       </c>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J169" s="12" t="inlineStr">
@@ -23819,7 +23819,7 @@
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H170" s="12" t="inlineStr">
@@ -23829,7 +23829,7 @@
       </c>
       <c r="I170" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J170" s="12" t="inlineStr">
@@ -23895,7 +23895,7 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H171" s="12" t="inlineStr">
@@ -23905,7 +23905,7 @@
       </c>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J171" s="12" t="inlineStr">
@@ -23968,7 +23968,7 @@
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H172" s="12" t="inlineStr">
@@ -23978,7 +23978,7 @@
       </c>
       <c r="I172" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="J172" s="12" t="inlineStr">
@@ -24045,7 +24045,7 @@
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H173" s="12" t="inlineStr">
@@ -24055,7 +24055,7 @@
       </c>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="J173" s="12" t="inlineStr">
@@ -24121,7 +24121,7 @@
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H174" s="12" t="inlineStr">
@@ -24131,7 +24131,7 @@
       </c>
       <c r="I174" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="J174" s="12" t="inlineStr">
@@ -24194,7 +24194,7 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H175" s="12" t="inlineStr">
@@ -24205,7 +24205,7 @@
       <c r="I175" s="12" t="inlineStr">
         <is>
           <t>The test lead removes the placement e-mail of INS-MPI in SIT.
-Data: TD-NB-05 Demo proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
+Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="J175" s="12" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H176" s="12" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="I176" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-03 Catalogue, insurers and TSU rules</t>
         </is>
       </c>
       <c r="J176" s="12" t="inlineStr">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H177" s="12" t="inlineStr">
@@ -24351,7 +24351,7 @@
       </c>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J177" s="12" t="inlineStr">
@@ -24418,7 +24418,7 @@
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H178" s="12" t="inlineStr">
@@ -24428,7 +24428,7 @@
       </c>
       <c r="I178" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J178" s="12" t="inlineStr">
@@ -24494,7 +24494,7 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H179" s="12" t="inlineStr">
@@ -24504,7 +24504,7 @@
       </c>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J179" s="12" t="inlineStr">
@@ -24571,7 +24571,7 @@
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H180" s="12" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="I180" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J180" s="12" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H181" s="12" t="inlineStr">
@@ -24658,7 +24658,7 @@
       </c>
       <c r="I181" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J181" s="12" t="inlineStr">
@@ -24721,7 +24721,7 @@
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H182" s="12" t="inlineStr">
@@ -24731,7 +24731,7 @@
       </c>
       <c r="I182" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J182" s="12" t="inlineStr">
@@ -24797,7 +24797,7 @@
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H183" s="12" t="inlineStr">
@@ -24807,7 +24807,7 @@
       </c>
       <c r="I183" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J183" s="12" t="inlineStr">
@@ -24873,7 +24873,7 @@
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H184" s="12" t="inlineStr">
@@ -24883,7 +24883,7 @@
       </c>
       <c r="I184" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J184" s="12" t="inlineStr">
@@ -24903,7 +24903,7 @@
       </c>
       <c r="M184" s="12" t="inlineStr">
         <is>
-          <t>QuotationProposalApiIT#demoProposalReadsAndTsuEndpoints</t>
+          <t>QuotationProposalApiIT#seedProposalReadsAndTsuEndpoints</t>
         </is>
       </c>
       <c r="N184" s="27" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H185" s="12" t="inlineStr">
@@ -24959,7 +24959,7 @@
       </c>
       <c r="I185" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J185" s="12" t="inlineStr">
@@ -24980,7 +24980,7 @@
       </c>
       <c r="M185" s="12" t="inlineStr">
         <is>
-          <t>QuotationProposalApiIT#demoProposalReadsAndTsuEndpoints</t>
+          <t>QuotationProposalApiIT#seedProposalReadsAndTsuEndpoints</t>
         </is>
       </c>
       <c r="N185" s="27" t="inlineStr">
@@ -25026,7 +25026,7 @@
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H186" s="12" t="inlineStr">
@@ -25036,7 +25036,7 @@
       </c>
       <c r="I186" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J186" s="12" t="inlineStr">
@@ -25103,7 +25103,7 @@
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H187" s="12" t="inlineStr">
@@ -25113,7 +25113,7 @@
       </c>
       <c r="I187" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J187" s="12" t="inlineStr">
@@ -25179,7 +25179,7 @@
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H188" s="12" t="inlineStr">
@@ -25189,7 +25189,7 @@
       </c>
       <c r="I188" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J188" s="12" t="inlineStr">
@@ -25251,7 +25251,7 @@
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H189" s="12" t="inlineStr">
@@ -25261,7 +25261,7 @@
       </c>
       <c r="I189" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J189" s="12" t="inlineStr">
@@ -25324,7 +25324,7 @@
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="H190" s="12" t="inlineStr">
@@ -25334,7 +25334,7 @@
       </c>
       <c r="I190" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF)</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="J190" s="12" t="inlineStr">
@@ -25397,7 +25397,7 @@
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H191" s="12" t="inlineStr">
@@ -25407,7 +25407,7 @@
       </c>
       <c r="I191" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF); TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J191" s="12" t="inlineStr">
@@ -25474,7 +25474,7 @@
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H192" s="12" t="inlineStr">
@@ -25484,7 +25484,7 @@
       </c>
       <c r="I192" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF); TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J192" s="12" t="inlineStr">
@@ -25551,7 +25551,7 @@
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H193" s="12" t="inlineStr">
@@ -25561,7 +25561,7 @@
       </c>
       <c r="I193" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-05 Demo proposal requests (PRF); TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J193" s="12" t="inlineStr">
@@ -25624,7 +25624,7 @@
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H194" s="12" t="inlineStr">
@@ -25635,7 +25635,7 @@
       <c r="I194" s="12" t="inlineStr">
         <is>
           <t>An accepted PRF of prospect PR-2026-000008 (Bayside Builders Co.).
-Data: TD-NB-05 Demo proposal requests (PRF); TD-NB-12 Documents to upload</t>
+Data: TD-NB-05 Seed proposal requests (PRF); TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J194" s="12" t="inlineStr">
@@ -25698,7 +25698,7 @@
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H195" s="12" t="inlineStr">
@@ -25708,7 +25708,7 @@
       </c>
       <c r="I195" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J195" s="12" t="inlineStr">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H196" s="12" t="inlineStr">
@@ -25780,7 +25780,7 @@
       </c>
       <c r="I196" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J196" s="12" t="inlineStr">
@@ -25842,7 +25842,7 @@
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H197" s="12" t="inlineStr">
@@ -25852,7 +25852,7 @@
       </c>
       <c r="I197" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J197" s="12" t="inlineStr">
@@ -25918,7 +25918,7 @@
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H198" s="12" t="inlineStr">
@@ -25928,7 +25928,7 @@
       </c>
       <c r="I198" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J198" s="12" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H199" s="12" t="inlineStr">
@@ -26000,7 +26000,7 @@
       </c>
       <c r="I199" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J199" s="12" t="inlineStr">
@@ -26063,7 +26063,7 @@
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H200" s="12" t="inlineStr">
@@ -26073,7 +26073,7 @@
       </c>
       <c r="I200" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-14 New records keyed in the test</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-14 New records keyed in the test</t>
         </is>
       </c>
       <c r="J200" s="12" t="inlineStr">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H201" s="12" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="I201" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-14 New records keyed in the test</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-14 New records keyed in the test</t>
         </is>
       </c>
       <c r="J201" s="12" t="inlineStr">
@@ -26216,7 +26216,7 @@
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H202" s="12" t="inlineStr">
@@ -26226,7 +26226,7 @@
       </c>
       <c r="I202" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-14 New records keyed in the test</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-14 New records keyed in the test</t>
         </is>
       </c>
       <c r="J202" s="12" t="inlineStr">
@@ -26293,7 +26293,7 @@
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H203" s="12" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="I203" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-14 New records keyed in the test</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-14 New records keyed in the test</t>
         </is>
       </c>
       <c r="J203" s="12" t="inlineStr">
@@ -26370,7 +26370,7 @@
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H204" s="12" t="inlineStr">
@@ -26380,7 +26380,7 @@
       </c>
       <c r="I204" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-14 New records keyed in the test</t>
+          <t>Data: TD-NB-02 Seed clients; TD-NB-03 Catalogue, insurers and TSU rules; TD-NB-14 New records keyed in the test</t>
         </is>
       </c>
       <c r="J204" s="12" t="inlineStr">
@@ -26443,7 +26443,7 @@
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H205" s="12" t="inlineStr">
@@ -26519,7 +26519,7 @@
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H206" s="12" t="inlineStr">
@@ -26595,7 +26595,7 @@
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H207" s="12" t="inlineStr">
@@ -26671,7 +26671,7 @@
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H208" s="12" t="inlineStr">
@@ -26747,7 +26747,7 @@
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H209" s="12" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H210" s="12" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H211" s="12" t="inlineStr">
@@ -26974,7 +26974,7 @@
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H212" s="12" t="inlineStr">
@@ -26984,7 +26984,7 @@
       </c>
       <c r="I212" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J212" s="12" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H213" s="12" t="inlineStr">
@@ -27061,7 +27061,7 @@
       </c>
       <c r="I213" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J213" s="12" t="inlineStr">
@@ -27127,7 +27127,7 @@
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H214" s="12" t="inlineStr">
@@ -27137,7 +27137,7 @@
       </c>
       <c r="I214" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J214" s="12" t="inlineStr">
@@ -27204,7 +27204,7 @@
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H215" s="12" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="I215" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J215" s="12" t="inlineStr">
@@ -27276,7 +27276,7 @@
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H216" s="12" t="inlineStr">
@@ -27286,7 +27286,7 @@
       </c>
       <c r="I216" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J216" s="12" t="inlineStr">
@@ -27353,7 +27353,7 @@
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H217" s="12" t="inlineStr">
@@ -27363,7 +27363,7 @@
       </c>
       <c r="I217" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J217" s="12" t="inlineStr">
@@ -27429,7 +27429,7 @@
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H218" s="12" t="inlineStr">
@@ -27439,7 +27439,7 @@
       </c>
       <c r="I218" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J218" s="12" t="inlineStr">
@@ -27502,7 +27502,7 @@
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H219" s="12" t="inlineStr">
@@ -27513,7 +27513,7 @@
       <c r="I219" s="12" t="inlineStr">
         <is>
           <t>A submitted account of prospect PR-2026-000010.
-Data: TD-NB-06 Demo accounts; TD-NB-12 Documents to upload</t>
+Data: TD-NB-06 Seed accounts; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J219" s="12" t="inlineStr">
@@ -27580,7 +27580,7 @@
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H220" s="12" t="inlineStr">
@@ -27590,7 +27590,7 @@
       </c>
       <c r="I220" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J220" s="12" t="inlineStr">
@@ -27656,7 +27656,7 @@
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H221" s="12" t="inlineStr">
@@ -27732,7 +27732,7 @@
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H222" s="12" t="inlineStr">
@@ -27808,7 +27808,7 @@
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H223" s="12" t="inlineStr">
@@ -27818,7 +27818,7 @@
       </c>
       <c r="I223" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J223" s="12" t="inlineStr">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H224" s="12" t="inlineStr">
@@ -27958,7 +27958,7 @@
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H225" s="12" t="inlineStr">
@@ -28031,7 +28031,7 @@
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H226" s="12" t="inlineStr">
@@ -28041,7 +28041,7 @@
       </c>
       <c r="I226" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J226" s="12" t="inlineStr">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
-          <t>EPOLICY_SENDER – E-policy Sender (demo user epol)</t>
+          <t>EPOLICY_SENDER – E-policy Sender (SIT/UAT user epol)</t>
         </is>
       </c>
       <c r="H227" s="12" t="inlineStr">
@@ -28118,7 +28118,7 @@
       <c r="I227" s="12" t="inlineStr">
         <is>
           <t>An issued account whose contact e-mail differs from the client e-mail.
-Data: TD-NB-02 Demo clients</t>
+Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J227" s="12" t="inlineStr">
@@ -28184,7 +28184,7 @@
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H228" s="12" t="inlineStr">
@@ -28194,7 +28194,7 @@
       </c>
       <c r="I228" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-02 Demo clients</t>
+          <t>Data: TD-NB-02 Seed clients</t>
         </is>
       </c>
       <c r="J228" s="12" t="inlineStr">
@@ -28257,7 +28257,7 @@
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H229" s="12" t="inlineStr">
@@ -28267,7 +28267,7 @@
       </c>
       <c r="I229" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J229" s="12" t="inlineStr">
@@ -28334,7 +28334,7 @@
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H230" s="12" t="inlineStr">
@@ -28344,7 +28344,7 @@
       </c>
       <c r="I230" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J230" s="12" t="inlineStr">
@@ -28407,7 +28407,7 @@
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H231" s="12" t="inlineStr">
@@ -28417,7 +28417,7 @@
       </c>
       <c r="I231" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J231" s="12" t="inlineStr">
@@ -28483,7 +28483,7 @@
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H232" s="12" t="inlineStr">
@@ -28493,7 +28493,7 @@
       </c>
       <c r="I232" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J232" s="12" t="inlineStr">
@@ -28556,7 +28556,7 @@
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H233" s="12" t="inlineStr">
@@ -28567,7 +28567,7 @@
       <c r="I233" s="12" t="inlineStr">
         <is>
           <t>An active account on an FFY-eligible Motor product.
-Data: TD-NB-06 Demo accounts; TD-NB-11 Bulk upload files</t>
+Data: TD-NB-06 Seed accounts; TD-NB-11 Bulk upload files</t>
         </is>
       </c>
       <c r="J233" s="12" t="inlineStr">
@@ -28633,7 +28633,7 @@
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H234" s="12" t="inlineStr">
@@ -28643,7 +28643,7 @@
       </c>
       <c r="I234" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-11 Bulk upload files</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-11 Bulk upload files</t>
         </is>
       </c>
       <c r="J234" s="12" t="inlineStr">
@@ -28709,7 +28709,7 @@
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H235" s="12" t="inlineStr">
@@ -28719,7 +28719,7 @@
       </c>
       <c r="I235" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-11 Bulk upload files</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-11 Bulk upload files</t>
         </is>
       </c>
       <c r="J235" s="12" t="inlineStr">
@@ -28786,7 +28786,7 @@
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H236" s="12" t="inlineStr">
@@ -28796,7 +28796,7 @@
       </c>
       <c r="I236" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-11 Bulk upload files</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-11 Bulk upload files</t>
         </is>
       </c>
       <c r="J236" s="12" t="inlineStr">
@@ -28863,7 +28863,7 @@
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H237" s="12" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="I237" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-11 Bulk upload files</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-11 Bulk upload files</t>
         </is>
       </c>
       <c r="J237" s="12" t="inlineStr">
@@ -28936,7 +28936,7 @@
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H238" s="12" t="inlineStr">
@@ -28947,7 +28947,7 @@
       <c r="I238" s="12" t="inlineStr">
         <is>
           <t>An account on an eligible product with Payment = Direct payment.
-Data: TD-NB-04 Demo quotations and requests; TD-NB-06 Demo accounts</t>
+Data: TD-NB-04 Seed quotations and requests; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J238" s="12" t="inlineStr">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H239" s="12" t="inlineStr">
@@ -29023,7 +29023,7 @@
       </c>
       <c r="I239" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J239" s="12" t="inlineStr">
@@ -29089,7 +29089,7 @@
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H240" s="12" t="inlineStr">
@@ -29099,7 +29099,7 @@
       </c>
       <c r="I240" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J240" s="12" t="inlineStr">
@@ -29166,7 +29166,7 @@
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H241" s="12" t="inlineStr">
@@ -29176,7 +29176,7 @@
       </c>
       <c r="I241" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-04 Seed quotations and requests; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J241" s="12" t="inlineStr">
@@ -29243,7 +29243,7 @@
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H242" s="12" t="inlineStr">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="I242" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J242" s="12" t="inlineStr">
@@ -29319,7 +29319,7 @@
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H243" s="12" t="inlineStr">
@@ -29329,7 +29329,7 @@
       </c>
       <c r="I243" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J243" s="12" t="inlineStr">
@@ -29396,7 +29396,7 @@
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H244" s="12" t="inlineStr">
@@ -29406,7 +29406,7 @@
       </c>
       <c r="I244" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J244" s="12" t="inlineStr">
@@ -29473,7 +29473,7 @@
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H245" s="12" t="inlineStr">
@@ -29483,7 +29483,7 @@
       </c>
       <c r="I245" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J245" s="12" t="inlineStr">
@@ -29549,7 +29549,7 @@
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H246" s="12" t="inlineStr">
@@ -29559,7 +29559,7 @@
       </c>
       <c r="I246" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J246" s="12" t="inlineStr">
@@ -29626,7 +29626,7 @@
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H247" s="12" t="inlineStr">
@@ -29636,7 +29636,7 @@
       </c>
       <c r="I247" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J247" s="12" t="inlineStr">
@@ -29702,7 +29702,7 @@
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H248" s="12" t="inlineStr">
@@ -29713,7 +29713,7 @@
       <c r="I248" s="12" t="inlineStr">
         <is>
           <t>The relay refuses the insurer address (set up by the test lead).
-Data: TD-NB-07 Demo placement and billing</t>
+Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J248" s="12" t="inlineStr">
@@ -29779,7 +29779,7 @@
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H249" s="12" t="inlineStr">
@@ -29789,7 +29789,7 @@
       </c>
       <c r="I249" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J249" s="12" t="inlineStr">
@@ -29856,7 +29856,7 @@
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H250" s="12" t="inlineStr">
@@ -29866,7 +29866,7 @@
       </c>
       <c r="I250" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J250" s="12" t="inlineStr">
@@ -29932,7 +29932,7 @@
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H251" s="12" t="inlineStr">
@@ -29942,7 +29942,7 @@
       </c>
       <c r="I251" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J251" s="12" t="inlineStr">
@@ -30009,7 +30009,7 @@
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H252" s="12" t="inlineStr">
@@ -30019,7 +30019,7 @@
       </c>
       <c r="I252" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J252" s="12" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="G253" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H253" s="12" t="inlineStr">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="I253" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J253" s="12" t="inlineStr">
@@ -30163,7 +30163,7 @@
       </c>
       <c r="G254" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H254" s="12" t="inlineStr">
@@ -30173,7 +30173,7 @@
       </c>
       <c r="I254" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J254" s="12" t="inlineStr">
@@ -30239,7 +30239,7 @@
       </c>
       <c r="G255" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H255" s="12" t="inlineStr">
@@ -30249,7 +30249,7 @@
       </c>
       <c r="I255" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J255" s="12" t="inlineStr">
@@ -30316,7 +30316,7 @@
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H256" s="12" t="inlineStr">
@@ -30326,7 +30326,7 @@
       </c>
       <c r="I256" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J256" s="12" t="inlineStr">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H257" s="12" t="inlineStr">
@@ -30403,7 +30403,7 @@
       </c>
       <c r="I257" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J257" s="12" t="inlineStr">
@@ -30470,7 +30470,7 @@
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H258" s="12" t="inlineStr">
@@ -30480,7 +30480,7 @@
       </c>
       <c r="I258" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J258" s="12" t="inlineStr">
@@ -30546,7 +30546,7 @@
       </c>
       <c r="G259" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H259" s="12" t="inlineStr">
@@ -30556,7 +30556,7 @@
       </c>
       <c r="I259" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J259" s="12" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H260" s="12" t="inlineStr">
@@ -30632,7 +30632,7 @@
       </c>
       <c r="I260" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J260" s="12" t="inlineStr">
@@ -30695,7 +30695,7 @@
       </c>
       <c r="G261" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H261" s="12" t="inlineStr">
@@ -30705,7 +30705,7 @@
       </c>
       <c r="I261" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J261" s="12" t="inlineStr">
@@ -30772,7 +30772,7 @@
       </c>
       <c r="G262" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H262" s="12" t="inlineStr">
@@ -30782,7 +30782,7 @@
       </c>
       <c r="I262" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J262" s="12" t="inlineStr">
@@ -30848,7 +30848,7 @@
       </c>
       <c r="G263" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H263" s="12" t="inlineStr">
@@ -30858,7 +30858,7 @@
       </c>
       <c r="I263" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J263" s="12" t="inlineStr">
@@ -30924,7 +30924,7 @@
       </c>
       <c r="G264" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H264" s="12" t="inlineStr">
@@ -30934,7 +30934,7 @@
       </c>
       <c r="I264" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J264" s="12" t="inlineStr">
@@ -31001,7 +31001,7 @@
       </c>
       <c r="G265" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H265" s="12" t="inlineStr">
@@ -31011,7 +31011,7 @@
       </c>
       <c r="I265" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J265" s="12" t="inlineStr">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="G266" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H266" s="12" t="inlineStr">
@@ -31084,7 +31084,7 @@
       </c>
       <c r="I266" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J266" s="12" t="inlineStr">
@@ -31150,7 +31150,7 @@
       </c>
       <c r="G267" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H267" s="12" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="I267" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J267" s="12" t="inlineStr">
@@ -31222,7 +31222,7 @@
       </c>
       <c r="G268" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H268" s="12" t="inlineStr">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="I268" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J268" s="12" t="inlineStr">
@@ -31295,7 +31295,7 @@
       </c>
       <c r="G269" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H269" s="12" t="inlineStr">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="I269" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J269" s="12" t="inlineStr">
@@ -31371,7 +31371,7 @@
       </c>
       <c r="G270" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H270" s="12" t="inlineStr">
@@ -31381,7 +31381,7 @@
       </c>
       <c r="I270" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J270" s="12" t="inlineStr">
@@ -31447,7 +31447,7 @@
       </c>
       <c r="G271" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H271" s="12" t="inlineStr">
@@ -31457,7 +31457,7 @@
       </c>
       <c r="I271" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J271" s="12" t="inlineStr">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="G272" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H272" s="12" t="inlineStr">
@@ -31534,7 +31534,7 @@
       </c>
       <c r="I272" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J272" s="12" t="inlineStr">
@@ -31601,7 +31601,7 @@
       </c>
       <c r="G273" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H273" s="12" t="inlineStr">
@@ -31611,7 +31611,7 @@
       </c>
       <c r="I273" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-13 E-policy and payment report files</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-13 E-policy and payment report files</t>
         </is>
       </c>
       <c r="J273" s="12" t="inlineStr">
@@ -31677,7 +31677,7 @@
       </c>
       <c r="G274" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H274" s="12" t="inlineStr">
@@ -31687,7 +31687,7 @@
       </c>
       <c r="I274" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-13 E-policy and payment report files</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-13 E-policy and payment report files</t>
         </is>
       </c>
       <c r="J274" s="12" t="inlineStr">
@@ -31753,7 +31753,7 @@
       </c>
       <c r="G275" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H275" s="12" t="inlineStr">
@@ -31763,7 +31763,7 @@
       </c>
       <c r="I275" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-13 E-policy and payment report files</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-13 E-policy and payment report files</t>
         </is>
       </c>
       <c r="J275" s="12" t="inlineStr">
@@ -31830,7 +31830,7 @@
       </c>
       <c r="G276" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H276" s="12" t="inlineStr">
@@ -31840,7 +31840,7 @@
       </c>
       <c r="I276" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-13 E-policy and payment report files</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-13 E-policy and payment report files</t>
         </is>
       </c>
       <c r="J276" s="12" t="inlineStr">
@@ -31907,7 +31907,7 @@
       </c>
       <c r="G277" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H277" s="12" t="inlineStr">
@@ -31917,7 +31917,7 @@
       </c>
       <c r="I277" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-13 E-policy and payment report files</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-13 E-policy and payment report files</t>
         </is>
       </c>
       <c r="J277" s="12" t="inlineStr">
@@ -31984,7 +31984,7 @@
       </c>
       <c r="G278" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H278" s="12" t="inlineStr">
@@ -31994,7 +31994,7 @@
       </c>
       <c r="I278" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-13 E-policy and payment report files</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-13 E-policy and payment report files</t>
         </is>
       </c>
       <c r="J278" s="12" t="inlineStr">
@@ -32061,7 +32061,7 @@
       </c>
       <c r="G279" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H279" s="12" t="inlineStr">
@@ -32071,7 +32071,7 @@
       </c>
       <c r="I279" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J279" s="12" t="inlineStr">
@@ -32138,7 +32138,7 @@
       </c>
       <c r="G280" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H280" s="12" t="inlineStr">
@@ -32148,7 +32148,7 @@
       </c>
       <c r="I280" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J280" s="12" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="G281" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H281" s="12" t="inlineStr">
@@ -32224,7 +32224,7 @@
       </c>
       <c r="I281" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J281" s="12" t="inlineStr">
@@ -32290,7 +32290,7 @@
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H282" s="12" t="inlineStr">
@@ -32300,7 +32300,7 @@
       </c>
       <c r="I282" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J282" s="12" t="inlineStr">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="G283" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H283" s="12" t="inlineStr">
@@ -32377,7 +32377,7 @@
       </c>
       <c r="I283" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-13 E-policy and payment report files</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-13 E-policy and payment report files</t>
         </is>
       </c>
       <c r="J283" s="12" t="inlineStr">
@@ -32443,7 +32443,7 @@
       </c>
       <c r="G284" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H284" s="12" t="inlineStr">
@@ -32453,7 +32453,7 @@
       </c>
       <c r="I284" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J284" s="12" t="inlineStr">
@@ -32520,7 +32520,7 @@
       </c>
       <c r="G285" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H285" s="12" t="inlineStr">
@@ -32530,7 +32530,7 @@
       </c>
       <c r="I285" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-13 E-policy and payment report files</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-13 E-policy and payment report files</t>
         </is>
       </c>
       <c r="J285" s="12" t="inlineStr">
@@ -32597,7 +32597,7 @@
       </c>
       <c r="G286" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H286" s="12" t="inlineStr">
@@ -32607,7 +32607,7 @@
       </c>
       <c r="I286" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-13 E-policy and payment report files</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-13 E-policy and payment report files</t>
         </is>
       </c>
       <c r="J286" s="12" t="inlineStr">
@@ -32674,7 +32674,7 @@
       </c>
       <c r="G287" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H287" s="12" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="I287" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-08 Demo issuance; TD-NB-13 E-policy and payment report files</t>
+          <t>Data: TD-NB-08 Seed issuance; TD-NB-13 E-policy and payment report files</t>
         </is>
       </c>
       <c r="J287" s="12" t="inlineStr">
@@ -32750,7 +32750,7 @@
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H288" s="12" t="inlineStr">
@@ -32827,7 +32827,7 @@
       </c>
       <c r="G289" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H289" s="12" t="inlineStr">
@@ -32837,7 +32837,7 @@
       </c>
       <c r="I289" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-08 Demo issuance; TD-NB-13 E-policy and payment report files</t>
+          <t>Data: TD-NB-08 Seed issuance; TD-NB-13 E-policy and payment report files</t>
         </is>
       </c>
       <c r="J289" s="12" t="inlineStr">
@@ -32904,7 +32904,7 @@
       </c>
       <c r="G290" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H290" s="12" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="I290" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-08 Demo issuance; TD-NB-13 E-policy and payment report files</t>
+          <t>Data: TD-NB-08 Seed issuance; TD-NB-13 E-policy and payment report files</t>
         </is>
       </c>
       <c r="J290" s="12" t="inlineStr">
@@ -32980,7 +32980,7 @@
       </c>
       <c r="G291" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H291" s="12" t="inlineStr">
@@ -32990,7 +32990,7 @@
       </c>
       <c r="I291" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-13 E-policy and payment report files</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-13 E-policy and payment report files</t>
         </is>
       </c>
       <c r="J291" s="12" t="inlineStr">
@@ -33056,7 +33056,7 @@
       </c>
       <c r="G292" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H292" s="12" t="inlineStr">
@@ -33066,7 +33066,7 @@
       </c>
       <c r="I292" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing; TD-NB-13 E-policy and payment report files</t>
+          <t>Data: TD-NB-07 Seed placement and billing; TD-NB-13 E-policy and payment report files</t>
         </is>
       </c>
       <c r="J292" s="12" t="inlineStr">
@@ -33128,7 +33128,7 @@
       </c>
       <c r="G293" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H293" s="12" t="inlineStr">
@@ -33139,7 +33139,7 @@
       <c r="I293" s="12" t="inlineStr">
         <is>
           <t>A placed mortgaged account (mortgagee bank set) with an e-policy in review.
-Data: TD-NB-08 Demo issuance</t>
+Data: TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J293" s="12" t="inlineStr">
@@ -33205,7 +33205,7 @@
       </c>
       <c r="G294" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H294" s="12" t="inlineStr">
@@ -33215,7 +33215,7 @@
       </c>
       <c r="I294" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-08 Demo issuance</t>
+          <t>Data: TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J294" s="12" t="inlineStr">
@@ -33282,7 +33282,7 @@
       </c>
       <c r="G295" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H295" s="12" t="inlineStr">
@@ -33292,7 +33292,7 @@
       </c>
       <c r="I295" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J295" s="12" t="inlineStr">
@@ -33359,7 +33359,7 @@
       </c>
       <c r="G296" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H296" s="12" t="inlineStr">
@@ -33369,7 +33369,7 @@
       </c>
       <c r="I296" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-08 Demo issuance</t>
+          <t>Data: TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J296" s="12" t="inlineStr">
@@ -33435,7 +33435,7 @@
       </c>
       <c r="G297" s="12" t="inlineStr">
         <is>
-          <t>EPOLICY_SENDER – E-policy Sender (demo user epol)</t>
+          <t>EPOLICY_SENDER – E-policy Sender (SIT/UAT user epol)</t>
         </is>
       </c>
       <c r="H297" s="12" t="inlineStr">
@@ -33445,7 +33445,7 @@
       </c>
       <c r="I297" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-08 Demo issuance</t>
+          <t>Data: TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J297" s="12" t="inlineStr">
@@ -33511,7 +33511,7 @@
       </c>
       <c r="G298" s="12" t="inlineStr">
         <is>
-          <t>EPOLICY_SENDER – E-policy Sender (demo user epol)</t>
+          <t>EPOLICY_SENDER – E-policy Sender (SIT/UAT user epol)</t>
         </is>
       </c>
       <c r="H298" s="12" t="inlineStr">
@@ -33521,7 +33521,7 @@
       </c>
       <c r="I298" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-08 Demo issuance</t>
+          <t>Data: TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J298" s="12" t="inlineStr">
@@ -33588,7 +33588,7 @@
       </c>
       <c r="G299" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H299" s="12" t="inlineStr">
@@ -33598,7 +33598,7 @@
       </c>
       <c r="I299" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-08 Demo issuance</t>
+          <t>Data: TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J299" s="12" t="inlineStr">
@@ -33661,7 +33661,7 @@
       </c>
       <c r="G300" s="12" t="inlineStr">
         <is>
-          <t>EPOLICY_SENDER – E-policy Sender (demo user epol)</t>
+          <t>EPOLICY_SENDER – E-policy Sender (SIT/UAT user epol)</t>
         </is>
       </c>
       <c r="H300" s="12" t="inlineStr">
@@ -33671,7 +33671,7 @@
       </c>
       <c r="I300" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-08 Demo issuance</t>
+          <t>Data: TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J300" s="12" t="inlineStr">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="G301" s="12" t="inlineStr">
         <is>
-          <t>EPOLICY_SENDER – E-policy Sender (demo user epol)</t>
+          <t>EPOLICY_SENDER – E-policy Sender (SIT/UAT user epol)</t>
         </is>
       </c>
       <c r="H301" s="12" t="inlineStr">
@@ -33747,7 +33747,7 @@
       </c>
       <c r="I301" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-08 Demo issuance</t>
+          <t>Data: TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J301" s="12" t="inlineStr">
@@ -33810,7 +33810,7 @@
       </c>
       <c r="G302" s="12" t="inlineStr">
         <is>
-          <t>EPOLICY_SENDER – E-policy Sender (demo user epol)</t>
+          <t>EPOLICY_SENDER – E-policy Sender (SIT/UAT user epol)</t>
         </is>
       </c>
       <c r="H302" s="12" t="inlineStr">
@@ -33821,7 +33821,7 @@
       <c r="I302" s="12" t="inlineStr">
         <is>
           <t>An issued account without contact e-mail.
-Data: TD-NB-08 Demo issuance</t>
+Data: TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J302" s="12" t="inlineStr">
@@ -33888,7 +33888,7 @@
       </c>
       <c r="G303" s="12" t="inlineStr">
         <is>
-          <t>EPOLICY_SENDER – E-policy Sender (demo user epol)</t>
+          <t>EPOLICY_SENDER – E-policy Sender (SIT/UAT user epol)</t>
         </is>
       </c>
       <c r="H303" s="12" t="inlineStr">
@@ -33899,7 +33899,7 @@
       <c r="I303" s="12" t="inlineStr">
         <is>
           <t>One dispatch failed (relay refuses the address).
-Data: TD-NB-08 Demo issuance</t>
+Data: TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J303" s="12" t="inlineStr">
@@ -33965,7 +33965,7 @@
       </c>
       <c r="G304" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H304" s="12" t="inlineStr">
@@ -33975,7 +33975,7 @@
       </c>
       <c r="I304" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-08 Demo issuance</t>
+          <t>Data: TD-NB-08 Seed issuance</t>
         </is>
       </c>
       <c r="J304" s="12" t="inlineStr">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="G305" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H305" s="12" t="inlineStr">
@@ -34048,12 +34048,12 @@
       </c>
       <c r="I305" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J305" s="12" t="inlineStr">
         <is>
-          <t>1. Booking Workbench, Ready to Book; open a demo account ready to book; enter booking date today and the cost center; click Book.</t>
+          <t>1. Booking Workbench, Ready to Book; open a seed account ready to book; enter booking date today and the cost center; click Book.</t>
         </is>
       </c>
       <c r="K305" s="12" t="inlineStr">
@@ -34114,7 +34114,7 @@
       </c>
       <c r="G306" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H306" s="12" t="inlineStr">
@@ -34125,7 +34125,7 @@
       <c r="I306" s="12" t="inlineStr">
         <is>
           <t>In SIT the test lead disables the GL account of the booking rule.
-Data: TD-NB-09 Demo booking</t>
+Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J306" s="12" t="inlineStr">
@@ -34191,7 +34191,7 @@
       </c>
       <c r="G307" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H307" s="12" t="inlineStr">
@@ -34201,7 +34201,7 @@
       </c>
       <c r="I307" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J307" s="12" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="G308" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H308" s="12" t="inlineStr">
@@ -34278,7 +34278,7 @@
       </c>
       <c r="I308" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J308" s="12" t="inlineStr">
@@ -34345,7 +34345,7 @@
       </c>
       <c r="G309" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H309" s="12" t="inlineStr">
@@ -34355,7 +34355,7 @@
       </c>
       <c r="I309" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J309" s="12" t="inlineStr">
@@ -34418,7 +34418,7 @@
       </c>
       <c r="G310" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H310" s="12" t="inlineStr">
@@ -34428,7 +34428,7 @@
       </c>
       <c r="I310" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking; TD-NB-11 Bulk upload files</t>
+          <t>Data: TD-NB-09 Seed booking; TD-NB-11 Bulk upload files</t>
         </is>
       </c>
       <c r="J310" s="12" t="inlineStr">
@@ -34494,7 +34494,7 @@
       </c>
       <c r="G311" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H311" s="12" t="inlineStr">
@@ -34504,7 +34504,7 @@
       </c>
       <c r="I311" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking; TD-NB-11 Bulk upload files</t>
+          <t>Data: TD-NB-09 Seed booking; TD-NB-11 Bulk upload files</t>
         </is>
       </c>
       <c r="J311" s="12" t="inlineStr">
@@ -34571,7 +34571,7 @@
       </c>
       <c r="G312" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H312" s="12" t="inlineStr">
@@ -34581,7 +34581,7 @@
       </c>
       <c r="I312" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking; TD-NB-11 Bulk upload files</t>
+          <t>Data: TD-NB-09 Seed booking; TD-NB-11 Bulk upload files</t>
         </is>
       </c>
       <c r="J312" s="12" t="inlineStr">
@@ -34648,7 +34648,7 @@
       </c>
       <c r="G313" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H313" s="12" t="inlineStr">
@@ -34658,7 +34658,7 @@
       </c>
       <c r="I313" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking; TD-NB-11 Bulk upload files</t>
+          <t>Data: TD-NB-09 Seed booking; TD-NB-11 Bulk upload files</t>
         </is>
       </c>
       <c r="J313" s="12" t="inlineStr">
@@ -34724,7 +34724,7 @@
       </c>
       <c r="G314" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H314" s="12" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="I314" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking; TD-NB-11 Bulk upload files</t>
+          <t>Data: TD-NB-09 Seed booking; TD-NB-11 Bulk upload files</t>
         </is>
       </c>
       <c r="J314" s="12" t="inlineStr">
@@ -34744,7 +34744,7 @@
       </c>
       <c r="K314" s="12" t="inlineStr">
         <is>
-          <t>The queued demo account is booked by the run.</t>
+          <t>The queued seed account is booked by the run.</t>
         </is>
       </c>
       <c r="L314" s="12" t="inlineStr">
@@ -34800,7 +34800,7 @@
       </c>
       <c r="G315" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H315" s="12" t="inlineStr">
@@ -34810,7 +34810,7 @@
       </c>
       <c r="I315" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J315" s="12" t="inlineStr">
@@ -34877,7 +34877,7 @@
       </c>
       <c r="G316" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H316" s="12" t="inlineStr">
@@ -34887,7 +34887,7 @@
       </c>
       <c r="I316" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J316" s="12" t="inlineStr">
@@ -34949,7 +34949,7 @@
       </c>
       <c r="G317" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H317" s="12" t="inlineStr">
@@ -34959,7 +34959,7 @@
       </c>
       <c r="I317" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J317" s="12" t="inlineStr">
@@ -35026,7 +35026,7 @@
       </c>
       <c r="G318" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H318" s="12" t="inlineStr">
@@ -35036,7 +35036,7 @@
       </c>
       <c r="I318" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J318" s="12" t="inlineStr">
@@ -35103,7 +35103,7 @@
       </c>
       <c r="G319" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H319" s="12" t="inlineStr">
@@ -35113,7 +35113,7 @@
       </c>
       <c r="I319" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-12 Documents to upload</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-12 Documents to upload</t>
         </is>
       </c>
       <c r="J319" s="12" t="inlineStr">
@@ -35179,7 +35179,7 @@
       </c>
       <c r="G320" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H320" s="12" t="inlineStr">
@@ -35189,12 +35189,12 @@
       </c>
       <c r="I320" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J320" s="12" t="inlineStr">
         <is>
-          <t>1. Book the demo multi-year account; open Invoices of the Account.</t>
+          <t>1. Book the seed multi-year account; open Invoices of the Account.</t>
         </is>
       </c>
       <c r="K320" s="12" t="inlineStr">
@@ -35255,7 +35255,7 @@
       </c>
       <c r="G321" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H321" s="12" t="inlineStr">
@@ -35265,7 +35265,7 @@
       </c>
       <c r="I321" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J321" s="12" t="inlineStr">
@@ -35328,7 +35328,7 @@
       </c>
       <c r="G322" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H322" s="12" t="inlineStr">
@@ -35339,7 +35339,7 @@
       <c r="I322" s="12" t="inlineStr">
         <is>
           <t>The test lead sets the start of year 2 to today in SIT.
-Data: TD-NB-09 Demo booking</t>
+Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J322" s="12" t="inlineStr">
@@ -35405,7 +35405,7 @@
       </c>
       <c r="G323" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H323" s="12" t="inlineStr">
@@ -35415,7 +35415,7 @@
       </c>
       <c r="I323" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J323" s="12" t="inlineStr">
@@ -35481,7 +35481,7 @@
       </c>
       <c r="G324" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H324" s="12" t="inlineStr">
@@ -35491,7 +35491,7 @@
       </c>
       <c r="I324" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J324" s="12" t="inlineStr">
@@ -35557,7 +35557,7 @@
       </c>
       <c r="G325" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H325" s="12" t="inlineStr">
@@ -35567,7 +35567,7 @@
       </c>
       <c r="I325" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J325" s="12" t="inlineStr">
@@ -35634,7 +35634,7 @@
       </c>
       <c r="G326" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H326" s="12" t="inlineStr">
@@ -35644,7 +35644,7 @@
       </c>
       <c r="I326" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J326" s="12" t="inlineStr">
@@ -35711,7 +35711,7 @@
       </c>
       <c r="G327" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H327" s="12" t="inlineStr">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="I327" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J327" s="12" t="inlineStr">
@@ -35788,7 +35788,7 @@
       </c>
       <c r="G328" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H328" s="12" t="inlineStr">
@@ -35798,7 +35798,7 @@
       </c>
       <c r="I328" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J328" s="12" t="inlineStr">
@@ -35861,7 +35861,7 @@
       </c>
       <c r="G329" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H329" s="12" t="inlineStr">
@@ -35871,7 +35871,7 @@
       </c>
       <c r="I329" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J329" s="12" t="inlineStr">
@@ -35937,7 +35937,7 @@
       </c>
       <c r="G330" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H330" s="12" t="inlineStr">
@@ -35947,7 +35947,7 @@
       </c>
       <c r="I330" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J330" s="12" t="inlineStr">
@@ -36013,7 +36013,7 @@
       </c>
       <c r="G331" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H331" s="12" t="inlineStr">
@@ -36023,7 +36023,7 @@
       </c>
       <c r="I331" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J331" s="12" t="inlineStr">
@@ -36090,7 +36090,7 @@
       </c>
       <c r="G332" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H332" s="12" t="inlineStr">
@@ -36100,7 +36100,7 @@
       </c>
       <c r="I332" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J332" s="12" t="inlineStr">
@@ -36167,7 +36167,7 @@
       </c>
       <c r="G333" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H333" s="12" t="inlineStr">
@@ -36177,7 +36177,7 @@
       </c>
       <c r="I333" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J333" s="12" t="inlineStr">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="G334" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H334" s="12" t="inlineStr">
@@ -36254,7 +36254,7 @@
       <c r="I334" s="12" t="inlineStr">
         <is>
           <t>The relay refuses the insurer address.
-Data: TD-NB-09 Demo booking</t>
+Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J334" s="12" t="inlineStr">
@@ -36316,7 +36316,7 @@
       </c>
       <c r="G335" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H335" s="12" t="inlineStr">
@@ -36326,7 +36326,7 @@
       </c>
       <c r="I335" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J335" s="12" t="inlineStr">
@@ -36393,7 +36393,7 @@
       </c>
       <c r="G336" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H336" s="12" t="inlineStr">
@@ -36403,7 +36403,7 @@
       </c>
       <c r="I336" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J336" s="12" t="inlineStr">
@@ -36470,7 +36470,7 @@
       </c>
       <c r="G337" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H337" s="12" t="inlineStr">
@@ -36480,7 +36480,7 @@
       </c>
       <c r="I337" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J337" s="12" t="inlineStr">
@@ -36547,7 +36547,7 @@
       </c>
       <c r="G338" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H338" s="12" t="inlineStr">
@@ -36557,12 +36557,12 @@
       </c>
       <c r="I338" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J338" s="12" t="inlineStr">
         <is>
-          <t>1. Book an account on a Motor package covered by CPC2 (demo); open the invoice and the Booked Accounts Register.</t>
+          <t>1. Book an account on a Motor package covered by CPC2 (seed); open the invoice and the Booked Accounts Register.</t>
         </is>
       </c>
       <c r="K338" s="12" t="inlineStr">
@@ -36623,7 +36623,7 @@
       </c>
       <c r="G339" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H339" s="12" t="inlineStr">
@@ -36633,7 +36633,7 @@
       </c>
       <c r="I339" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J339" s="12" t="inlineStr">
@@ -36695,7 +36695,7 @@
       </c>
       <c r="G340" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H340" s="12" t="inlineStr">
@@ -36705,7 +36705,7 @@
       </c>
       <c r="I340" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J340" s="12" t="inlineStr">
@@ -36772,7 +36772,7 @@
       </c>
       <c r="G341" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H341" s="12" t="inlineStr">
@@ -36782,7 +36782,7 @@
       </c>
       <c r="I341" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J341" s="12" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="G342" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H342" s="12" t="inlineStr">
@@ -36859,7 +36859,7 @@
       </c>
       <c r="I342" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-09 Demo booking</t>
+          <t>Data: TD-NB-09 Seed booking</t>
         </is>
       </c>
       <c r="J342" s="12" t="inlineStr">
@@ -36925,7 +36925,7 @@
       </c>
       <c r="G343" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H343" s="12" t="inlineStr">
@@ -36935,7 +36935,7 @@
       </c>
       <c r="I343" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J343" s="12" t="inlineStr">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="G344" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H344" s="12" t="inlineStr">
@@ -37011,7 +37011,7 @@
       </c>
       <c r="I344" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J344" s="12" t="inlineStr">
@@ -37077,7 +37077,7 @@
       </c>
       <c r="G345" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H345" s="12" t="inlineStr">
@@ -37087,7 +37087,7 @@
       </c>
       <c r="I345" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J345" s="12" t="inlineStr">
@@ -37154,7 +37154,7 @@
       </c>
       <c r="G346" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H346" s="12" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="I346" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J346" s="12" t="inlineStr">
@@ -37230,7 +37230,7 @@
       </c>
       <c r="G347" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H347" s="12" t="inlineStr">
@@ -37240,7 +37240,7 @@
       </c>
       <c r="I347" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J347" s="12" t="inlineStr">
@@ -37306,7 +37306,7 @@
       </c>
       <c r="G348" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H348" s="12" t="inlineStr">
@@ -37316,7 +37316,7 @@
       </c>
       <c r="I348" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-07 Demo placement and billing</t>
+          <t>Data: TD-NB-07 Seed placement and billing</t>
         </is>
       </c>
       <c r="J348" s="12" t="inlineStr">
@@ -37379,7 +37379,7 @@
       </c>
       <c r="G349" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H349" s="12" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="I349" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-10 Report targets and variants</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-10 Report targets and variants</t>
         </is>
       </c>
       <c r="J349" s="12" t="inlineStr">
@@ -37455,7 +37455,7 @@
       </c>
       <c r="G350" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H350" s="12" t="inlineStr">
@@ -37465,7 +37465,7 @@
       </c>
       <c r="I350" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-10 Report targets and variants</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-10 Report targets and variants</t>
         </is>
       </c>
       <c r="J350" s="12" t="inlineStr">
@@ -37531,7 +37531,7 @@
       </c>
       <c r="G351" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H351" s="12" t="inlineStr">
@@ -37541,7 +37541,7 @@
       </c>
       <c r="I351" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-10 Report targets and variants</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-10 Report targets and variants</t>
         </is>
       </c>
       <c r="J351" s="12" t="inlineStr">
@@ -37603,7 +37603,7 @@
       </c>
       <c r="G352" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H352" s="12" t="inlineStr">
@@ -37613,7 +37613,7 @@
       </c>
       <c r="I352" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts; TD-NB-10 Report targets and variants</t>
+          <t>Data: TD-NB-06 Seed accounts; TD-NB-10 Report targets and variants</t>
         </is>
       </c>
       <c r="J352" s="12" t="inlineStr">
@@ -37680,7 +37680,7 @@
       </c>
       <c r="G353" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H353" s="12" t="inlineStr">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="G354" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H354" s="12" t="inlineStr">
@@ -37833,7 +37833,7 @@
       </c>
       <c r="G355" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H355" s="12" t="inlineStr">
@@ -37910,7 +37910,7 @@
       </c>
       <c r="G356" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H356" s="12" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="I356" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J356" s="12" t="inlineStr">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="G357" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H357" s="12" t="inlineStr">
@@ -37996,7 +37996,7 @@
       </c>
       <c r="I357" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J357" s="12" t="inlineStr">
@@ -38058,7 +38058,7 @@
       </c>
       <c r="G358" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H358" s="12" t="inlineStr">
@@ -38068,7 +38068,7 @@
       </c>
       <c r="I358" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J358" s="12" t="inlineStr">
@@ -38134,7 +38134,7 @@
       </c>
       <c r="G359" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H359" s="12" t="inlineStr">
@@ -38144,7 +38144,7 @@
       </c>
       <c r="I359" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-06 Demo accounts</t>
+          <t>Data: TD-NB-06 Seed accounts</t>
         </is>
       </c>
       <c r="J359" s="12" t="inlineStr">
@@ -38211,7 +38211,7 @@
       </c>
       <c r="G360" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H360" s="12" t="inlineStr">
@@ -38279,7 +38279,7 @@
       </c>
       <c r="G361" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H361" s="12" t="inlineStr">
@@ -38347,7 +38347,7 @@
       </c>
       <c r="G362" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H362" s="12" t="inlineStr">
@@ -38357,7 +38357,7 @@
       </c>
       <c r="I362" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J362" s="12" t="inlineStr">
@@ -38419,7 +38419,7 @@
       </c>
       <c r="G363" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H363" s="12" t="inlineStr">
@@ -38429,7 +38429,7 @@
       </c>
       <c r="I363" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J363" s="12" t="inlineStr">
@@ -38495,7 +38495,7 @@
       </c>
       <c r="G364" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H364" s="12" t="inlineStr">
@@ -38505,7 +38505,7 @@
       </c>
       <c r="I364" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J364" s="12" t="inlineStr">
@@ -38571,7 +38571,7 @@
       </c>
       <c r="G365" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H365" s="12" t="inlineStr">
@@ -38581,7 +38581,7 @@
       </c>
       <c r="I365" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J365" s="12" t="inlineStr">
@@ -38648,7 +38648,7 @@
       </c>
       <c r="G366" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="H366" s="12" t="inlineStr">
@@ -38659,7 +38659,7 @@
       <c r="I366" s="12" t="inlineStr">
         <is>
           <t>LOGIN_MAX_FAILED_ATTEMPTS is 3.
-Data: TD-NB-01 Demo users and roles</t>
+Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J366" s="12" t="inlineStr">
@@ -38726,7 +38726,7 @@
       </c>
       <c r="G367" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H367" s="12" t="inlineStr">
@@ -38736,7 +38736,7 @@
       </c>
       <c r="I367" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J367" s="12" t="inlineStr">
@@ -38802,7 +38802,7 @@
       </c>
       <c r="G368" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H368" s="12" t="inlineStr">
@@ -38812,7 +38812,7 @@
       </c>
       <c r="I368" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J368" s="12" t="inlineStr">
@@ -38878,7 +38878,7 @@
       </c>
       <c r="G369" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H369" s="12" t="inlineStr">
@@ -38888,7 +38888,7 @@
       </c>
       <c r="I369" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J369" s="12" t="inlineStr">
@@ -38955,7 +38955,7 @@
       </c>
       <c r="G370" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H370" s="12" t="inlineStr">
@@ -38965,7 +38965,7 @@
       </c>
       <c r="I370" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J370" s="12" t="inlineStr">
@@ -39031,7 +39031,7 @@
       </c>
       <c r="G371" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H371" s="12" t="inlineStr">
@@ -39041,7 +39041,7 @@
       </c>
       <c r="I371" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J371" s="12" t="inlineStr">
@@ -39108,7 +39108,7 @@
       </c>
       <c r="G372" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H372" s="12" t="inlineStr">
@@ -39118,7 +39118,7 @@
       </c>
       <c r="I372" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J372" s="12" t="inlineStr">
@@ -39185,7 +39185,7 @@
       </c>
       <c r="G373" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H373" s="12" t="inlineStr">
@@ -39195,7 +39195,7 @@
       </c>
       <c r="I373" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J373" s="12" t="inlineStr">
@@ -39258,7 +39258,7 @@
       </c>
       <c r="G374" s="12" t="inlineStr">
         <is>
-          <t>NB_APPROVER – New Business approver (demo user approver)</t>
+          <t>NB_APPROVER – New Business approver (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="H374" s="12" t="inlineStr">
@@ -39269,7 +39269,7 @@
       <c r="I374" s="12" t="inlineStr">
         <is>
           <t>badmin submitted an access request and a new list value.
-Data: TD-NB-01 Demo users and roles</t>
+Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J374" s="12" t="inlineStr">
@@ -39335,7 +39335,7 @@
       </c>
       <c r="G375" s="12" t="inlineStr">
         <is>
-          <t>NB_APPROVER – New Business approver (demo user approver)</t>
+          <t>NB_APPROVER – New Business approver (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="H375" s="12" t="inlineStr">
@@ -39345,7 +39345,7 @@
       </c>
       <c r="I375" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J375" s="12" t="inlineStr">
@@ -39412,7 +39412,7 @@
       </c>
       <c r="G376" s="12" t="inlineStr">
         <is>
-          <t>NB_APPROVER – New Business approver (demo user approver)</t>
+          <t>NB_APPROVER – New Business approver (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="H376" s="12" t="inlineStr">
@@ -39423,7 +39423,7 @@
       <c r="I376" s="12" t="inlineStr">
         <is>
           <t>A test user holding ACCESS_REQUEST and ACCESS_APPROVE submitted a request.
-Data: TD-NB-01 Demo users and roles</t>
+Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J376" s="12" t="inlineStr">
@@ -39490,7 +39490,7 @@
       </c>
       <c r="G377" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H377" s="12" t="inlineStr">
@@ -39500,7 +39500,7 @@
       </c>
       <c r="I377" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J377" s="12" t="inlineStr">
@@ -39566,7 +39566,7 @@
       </c>
       <c r="G378" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H378" s="12" t="inlineStr">
@@ -39576,7 +39576,7 @@
       </c>
       <c r="I378" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J378" s="12" t="inlineStr">
@@ -39643,7 +39643,7 @@
       </c>
       <c r="G379" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H379" s="12" t="inlineStr">
@@ -39653,7 +39653,7 @@
       </c>
       <c r="I379" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J379" s="12" t="inlineStr">
@@ -39719,7 +39719,7 @@
       </c>
       <c r="G380" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H380" s="12" t="inlineStr">
@@ -39729,7 +39729,7 @@
       </c>
       <c r="I380" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J380" s="12" t="inlineStr">
@@ -39796,7 +39796,7 @@
       </c>
       <c r="G381" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H381" s="12" t="inlineStr">
@@ -39806,7 +39806,7 @@
       </c>
       <c r="I381" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J381" s="12" t="inlineStr">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="G382" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H382" s="12" t="inlineStr">
@@ -39883,7 +39883,7 @@
       </c>
       <c r="I382" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J382" s="12" t="inlineStr">
@@ -39950,7 +39950,7 @@
       </c>
       <c r="G383" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H383" s="12" t="inlineStr">
@@ -39960,7 +39960,7 @@
       </c>
       <c r="I383" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J383" s="12" t="inlineStr">
@@ -40027,7 +40027,7 @@
       </c>
       <c r="G384" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H384" s="12" t="inlineStr">
@@ -40037,7 +40037,7 @@
       </c>
       <c r="I384" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J384" s="12" t="inlineStr">
@@ -40104,7 +40104,7 @@
       </c>
       <c r="G385" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H385" s="12" t="inlineStr">
@@ -40114,7 +40114,7 @@
       </c>
       <c r="I385" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J385" s="12" t="inlineStr">
@@ -40176,7 +40176,7 @@
       </c>
       <c r="G386" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="H386" s="12" t="inlineStr">
@@ -40186,7 +40186,7 @@
       </c>
       <c r="I386" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J386" s="12" t="inlineStr">
@@ -40249,7 +40249,7 @@
       </c>
       <c r="G387" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H387" s="12" t="inlineStr">
@@ -40259,7 +40259,7 @@
       </c>
       <c r="I387" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-01 Demo users and roles</t>
+          <t>Data: TD-NB-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J387" s="12" t="inlineStr">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="G388" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H388" s="12" t="inlineStr">
@@ -40335,7 +40335,7 @@
       </c>
       <c r="I388" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J388" s="12" t="inlineStr">
@@ -40401,7 +40401,7 @@
       </c>
       <c r="G389" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H389" s="12" t="inlineStr">
@@ -40411,7 +40411,7 @@
       </c>
       <c r="I389" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J389" s="12" t="inlineStr">
@@ -40478,7 +40478,7 @@
       </c>
       <c r="G390" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="H390" s="12" t="inlineStr">
@@ -40488,7 +40488,7 @@
       </c>
       <c r="I390" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-NB-04 Demo quotations and requests</t>
+          <t>Data: TD-NB-04 Seed quotations and requests</t>
         </is>
       </c>
       <c r="J390" s="12" t="inlineStr">
@@ -49318,17 +49318,17 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Demo users and roles</t>
+          <t>SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>ao and ao2 (MKT_AO), mkttl (MKT_TL), tsu and tsulead (TSU; two officers for four-eyes), proc (PROCESSOR), proctl (PROCESSING_TL), approver (NB_APPROVER), epol (EPOLICY_SENDER), adjust (ADJUSTMENT), badmin (BUSINESS_ADMIN), admin (SYSADMIN), auditor (AUDITOR). The demo password is issued by the test lead.</t>
+          <t>ao and ao2 (MKT_AO), mkttl (MKT_TL), tsu and tsulead (TSU; two officers for four-eyes), proc (PROCESSOR), proctl (PROCESSING_TL), approver (NB_APPROVER), epol (EPOLICY_SENDER), adjust (ADJUSTMENT), badmin (BUSINESS_ADMIN), admin (SYSADMIN), auditor (AUDITOR). The SIT/UAT password is issued by the test lead.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Demo seeds V980 (broking users), V900 (admin, auditor); roles and grants V750</t>
+          <t>Seeds V980 (broking users), V900 (admin, auditor); roles and grants V750</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -49343,7 +49343,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Demo clients</t>
+          <t>Seed clients</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -49353,7 +49353,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V981</t>
+          <t>Seed V981</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
@@ -49378,7 +49378,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V982 (catalogue, insurers, sales organisation); rates V811</t>
+          <t>Seed V982 (catalogue, insurers, sales organisation); rates V811</t>
         </is>
       </c>
       <c r="E7" s="12" t="n">
@@ -49393,7 +49393,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Demo quotations and requests</t>
+          <t>Seed quotations and requests</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -49403,7 +49403,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V984</t>
+          <t>Seed V984</t>
         </is>
       </c>
       <c r="E8" s="12" t="n">
@@ -49418,7 +49418,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Demo proposal requests (PRF)</t>
+          <t>Seed proposal requests (PRF)</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -49428,7 +49428,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V985</t>
+          <t>Seed V985</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
@@ -49443,7 +49443,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Demo accounts</t>
+          <t>Seed accounts</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -49453,7 +49453,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V983</t>
+          <t>Seed V983</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
@@ -49468,7 +49468,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Demo placement and billing</t>
+          <t>Seed placement and billing</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -49478,7 +49478,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V986</t>
+          <t>Seed V986</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
@@ -49493,7 +49493,7 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Demo issuance</t>
+          <t>Seed issuance</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -49503,7 +49503,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V987</t>
+          <t>Seed V987</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
@@ -49518,17 +49518,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Demo booking</t>
+          <t>Seed booking</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Seven accounts of CL-2026-000001 to 000006 in POLICY_ISSUED; four booked at start-up with one positive endorsement and one partial cancellation; one queued by the demo auto-book rule (PAR08 CBG); two ready to book, one of them multi-year</t>
+          <t>Seven accounts of CL-2026-000001 to 000006 in POLICY_ISSUED; four booked at start-up with one positive endorsement and one partial cancellation; one queued by the seed auto-book rule (PAR08 CBG); two ready to book, one of them multi-year</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V988 and the booking demo seeder</t>
+          <t>Seed V988 and the booking seed seeder</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
@@ -49553,7 +49553,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V989</t>
+          <t>Seed V989</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
@@ -49628,7 +49628,7 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Prepared by the test lead in the layouts of the demo files (PlacementFilesTest, EpolicyPdf)</t>
+          <t>Prepared by the test lead in the layouts of the seed files (PlacementFilesTest, EpolicyPdf)</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
@@ -49827,7 +49827,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -49878,7 +49878,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -49929,7 +49929,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -49980,7 +49980,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -50031,7 +50031,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -50082,7 +50082,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -50133,7 +50133,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -50184,7 +50184,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -50235,7 +50235,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -50286,7 +50286,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -50337,7 +50337,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -50388,7 +50388,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -50439,7 +50439,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>NB_APPROVER – New Business approver (demo user approver)</t>
+          <t>NB_APPROVER – New Business approver (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -50490,7 +50490,7 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -50541,7 +50541,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -50592,7 +50592,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>NB_APPROVER – New Business approver (demo user approver)</t>
+          <t>NB_APPROVER – New Business approver (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -50643,7 +50643,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -50694,7 +50694,7 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -50745,7 +50745,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -50792,7 +50792,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -50839,7 +50839,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -50886,7 +50886,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -50933,7 +50933,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -50984,7 +50984,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -51035,7 +51035,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -51086,7 +51086,7 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -51101,7 +51101,7 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>QuotationProposalApiIT#demoProposalReadsAndTsuEndpoints</t>
+          <t>QuotationProposalApiIT#seedProposalReadsAndTsuEndpoints</t>
         </is>
       </c>
       <c r="I30" s="27" t="inlineStr">
@@ -51137,7 +51137,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -51152,7 +51152,7 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>QuotationProposalApiIT#demoProposalReadsAndTsuEndpoints</t>
+          <t>QuotationProposalApiIT#seedProposalReadsAndTsuEndpoints</t>
         </is>
       </c>
       <c r="I31" s="27" t="inlineStr">
@@ -51188,7 +51188,7 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -51203,7 +51203,7 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>QuotationProposalApiIT#demoProposalReadsAndTsuEndpoints</t>
+          <t>QuotationProposalApiIT#seedProposalReadsAndTsuEndpoints</t>
         </is>
       </c>
       <c r="I32" s="27" t="inlineStr">
@@ -51239,7 +51239,7 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -51254,7 +51254,7 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>QuotationProposalApiIT#demoProposalReadsAndTsuEndpoints</t>
+          <t>QuotationProposalApiIT#seedProposalReadsAndTsuEndpoints</t>
         </is>
       </c>
       <c r="I33" s="27" t="inlineStr">
@@ -51290,7 +51290,7 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -51341,7 +51341,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -51392,7 +51392,7 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -51443,7 +51443,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>PROCESSING_TL – Processing TL (demo user proctl)</t>
+          <t>PROCESSING_TL – Processing TL (SIT/UAT user proctl)</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -51494,7 +51494,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>TSU – TSU officer (demo user tsu)</t>
+          <t>TSU – TSU officer (SIT/UAT user tsu)</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -51545,7 +51545,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>NB_APPROVER – New Business approver (demo user approver)</t>
+          <t>NB_APPROVER – New Business approver (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -51596,7 +51596,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>EPOLICY_SENDER – E-policy Sender (demo user epol)</t>
+          <t>EPOLICY_SENDER – E-policy Sender (SIT/UAT user epol)</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -51647,7 +51647,7 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -51698,7 +51698,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -51749,7 +51749,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>PROCESSING_TL – Processing TL (demo user proctl)</t>
+          <t>PROCESSING_TL – Processing TL (SIT/UAT user proctl)</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -51800,7 +51800,7 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -51851,7 +51851,7 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -51902,7 +51902,7 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -51953,7 +51953,7 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>PROCESSING_TL – Processing TL (demo user proctl)</t>
+          <t>PROCESSING_TL – Processing TL (SIT/UAT user proctl)</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -52004,7 +52004,7 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -52055,7 +52055,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -52106,7 +52106,7 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>EPOLICY_SENDER – E-policy Sender (demo user epol)</t>
+          <t>EPOLICY_SENDER – E-policy Sender (SIT/UAT user epol)</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -52157,7 +52157,7 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -52208,7 +52208,7 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>PROCESSING_TL – Processing TL (demo user proctl)</t>
+          <t>PROCESSING_TL – Processing TL (SIT/UAT user proctl)</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -52259,7 +52259,7 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -52310,7 +52310,7 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>NB_APPROVER – New Business approver (demo user approver)</t>
+          <t>NB_APPROVER – New Business approver (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -52361,7 +52361,7 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -52408,7 +52408,7 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>PROCESSING_TL – Processing TL (demo user proctl)</t>
+          <t>PROCESSING_TL – Processing TL (SIT/UAT user proctl)</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -52455,7 +52455,7 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -52502,7 +52502,7 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>EPOLICY_SENDER – E-policy Sender (demo user epol)</t>
+          <t>EPOLICY_SENDER – E-policy Sender (SIT/UAT user epol)</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -52549,7 +52549,7 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>EPOLICY_SENDER – E-policy Sender (demo user epol)</t>
+          <t>EPOLICY_SENDER – E-policy Sender (SIT/UAT user epol)</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -52596,7 +52596,7 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
@@ -52643,7 +52643,7 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -52690,7 +52690,7 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
@@ -52741,7 +52741,7 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>PROCESSING_TL – Processing TL (demo user proctl)</t>
+          <t>PROCESSING_TL – Processing TL (SIT/UAT user proctl)</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -52792,7 +52792,7 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -52843,7 +52843,7 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -52894,7 +52894,7 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
@@ -52945,7 +52945,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -52996,7 +52996,7 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -53047,7 +53047,7 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>PROCESSING_TL – Processing TL (demo user proctl)</t>
+          <t>PROCESSING_TL – Processing TL (SIT/UAT user proctl)</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -53098,7 +53098,7 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -53149,7 +53149,7 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -53200,7 +53200,7 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -53251,7 +53251,7 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -53302,7 +53302,7 @@
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
@@ -53353,7 +53353,7 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -53404,7 +53404,7 @@
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
@@ -53455,7 +53455,7 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -53506,7 +53506,7 @@
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>NB_APPROVER – New Business approver (demo user approver)</t>
+          <t>NB_APPROVER – New Business approver (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
@@ -53557,7 +53557,7 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>NB_APPROVER – New Business approver (demo user approver)</t>
+          <t>NB_APPROVER – New Business approver (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -53604,7 +53604,7 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
@@ -53651,7 +53651,7 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
@@ -53698,7 +53698,7 @@
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>BUSINESS_ADMIN – Business Administrator (demo user badmin)</t>
+          <t>BUSINESS_ADMIN – Business Administrator (SIT/UAT user badmin)</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
@@ -53745,7 +53745,7 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
@@ -53792,7 +53792,7 @@
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
@@ -53839,7 +53839,7 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
@@ -53886,7 +53886,7 @@
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / TH / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / TH / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
@@ -53937,7 +53937,7 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>PROCESSING_TL – Processing TL (demo user proctl)</t>
+          <t>PROCESSING_TL – Processing TL (SIT/UAT user proctl)</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -53988,7 +53988,7 @@
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>NB_APPROVER – New Business approver (demo user approver)</t>
+          <t>NB_APPROVER – New Business approver (SIT/UAT user approver)</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
@@ -54039,7 +54039,7 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>MKT_AO – Marketing AO (demo user ao)</t>
+          <t>MKT_AO – Marketing AO (SIT/UAT user ao)</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -54090,7 +54090,7 @@
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>PROCESSOR – Processing (demo user proc)</t>
+          <t>PROCESSOR – Processing (SIT/UAT user proc)</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">

--- a/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-01_New_Business_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-01_New_Business_v1.0.xlsx
@@ -49528,7 +49528,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Seed V988 and the booking seed seeder</t>
+          <t>Seed V988 and the booking seed runner (BookingSeedData)</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
